--- a/Test Results/Excel/Performance_Test_Report.xlsx
+++ b/Test Results/Excel/Performance_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,14 +41,8 @@
       <color rgb="00375623"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +59,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,14 +88,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -569,16 +556,16 @@
         <v>120</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -614,16 +601,16 @@
         <v>120</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -659,16 +646,16 @@
         <v>120</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -704,16 +691,16 @@
         <v>120</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -752,13 +739,13 @@
         <v>124</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -794,16 +781,16 @@
         <v>120</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -839,16 +826,16 @@
         <v>120</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -884,16 +871,16 @@
         <v>120</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -929,16 +916,16 @@
         <v>120</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -977,13 +964,13 @@
         <v>124</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1019,16 +1006,16 @@
         <v>120</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1064,25 +1051,25 @@
         <v>120</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1109,16 +1096,16 @@
         <v>120</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1154,16 +1141,16 @@
         <v>120</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1202,13 +1189,13 @@
         <v>124</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1244,16 +1231,16 @@
         <v>120</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1289,16 +1276,16 @@
         <v>120</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1334,16 +1321,16 @@
         <v>120</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1379,16 +1366,16 @@
         <v>120</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1427,13 +1414,13 @@
         <v>124</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -1469,16 +1456,16 @@
         <v>120</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -1514,16 +1501,16 @@
         <v>120</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1546,16 @@
         <v>120</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1604,25 +1591,25 @@
         <v>120</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1639,13 @@
         <v>124</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -1694,16 +1681,16 @@
         <v>120</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -1739,16 +1726,16 @@
         <v>120</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -1784,16 +1771,16 @@
         <v>120</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -1829,16 +1816,16 @@
         <v>120</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1864,13 @@
         <v>124</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -1919,16 +1906,16 @@
         <v>120</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -1964,16 +1951,16 @@
         <v>120</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2009,16 +1996,16 @@
         <v>120</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2054,16 +2041,16 @@
         <v>120</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -2102,13 +2089,13 @@
         <v>124</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -2144,25 +2131,25 @@
         <v>120</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2189,16 +2176,16 @@
         <v>120</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -2234,16 +2221,16 @@
         <v>120</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -2279,16 +2266,16 @@
         <v>120</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -2324,16 +2311,16 @@
         <v>120</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -2369,16 +2356,16 @@
         <v>120</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -2414,16 +2401,16 @@
         <v>120</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -2459,16 +2446,16 @@
         <v>120</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -2504,16 +2491,16 @@
         <v>120</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -2552,13 +2539,13 @@
         <v>124</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -2594,16 +2581,16 @@
         <v>120</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -2639,16 +2626,16 @@
         <v>120</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -2684,25 +2671,25 @@
         <v>120</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2729,16 +2716,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -2777,13 +2764,13 @@
         <v>124</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -2819,16 +2806,16 @@
         <v>120</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -2864,16 +2851,16 @@
         <v>120</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -2909,16 +2896,16 @@
         <v>120</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -2954,16 +2941,16 @@
         <v>120</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -3002,13 +2989,13 @@
         <v>124</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -3044,16 +3031,16 @@
         <v>120</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -3089,16 +3076,16 @@
         <v>120</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -3134,16 +3121,16 @@
         <v>120</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -3179,16 +3166,16 @@
         <v>120</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -3227,22 +3214,22 @@
         <v>124</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3269,16 +3256,16 @@
         <v>120</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -3314,16 +3301,16 @@
         <v>120</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -3359,16 +3346,16 @@
         <v>120</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -3404,16 +3391,16 @@
         <v>120</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -3452,13 +3439,13 @@
         <v>124</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -3494,16 +3481,16 @@
         <v>120</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -3539,16 +3526,16 @@
         <v>120</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -3584,16 +3571,16 @@
         <v>120</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -3629,16 +3616,16 @@
         <v>120</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -3677,13 +3664,13 @@
         <v>124</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -3719,16 +3706,16 @@
         <v>120</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -3764,25 +3751,25 @@
         <v>120</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K73" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3809,16 +3796,16 @@
         <v>120</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -3854,16 +3841,16 @@
         <v>120</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -3902,13 +3889,13 @@
         <v>124</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3931,16 @@
         <v>120</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -3989,16 +3976,16 @@
         <v>120</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
@@ -4034,16 +4021,16 @@
         <v>120</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -4079,16 +4066,16 @@
         <v>120</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -4124,16 +4111,16 @@
         <v>120</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -4169,16 +4156,16 @@
         <v>120</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -4214,16 +4201,16 @@
         <v>120</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -4259,16 +4246,16 @@
         <v>120</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -4304,25 +4291,25 @@
         <v>120</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K85" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4352,13 +4339,13 @@
         <v>124</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -4394,16 +4381,16 @@
         <v>120</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -4439,16 +4426,16 @@
         <v>120</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -4484,16 +4471,16 @@
         <v>120</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -4529,16 +4516,16 @@
         <v>120</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -4577,13 +4564,13 @@
         <v>124</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -4619,16 +4606,16 @@
         <v>120</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -4664,16 +4651,16 @@
         <v>120</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -4709,16 +4696,16 @@
         <v>120</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -4754,16 +4741,16 @@
         <v>120</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -4802,13 +4789,13 @@
         <v>124</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -4844,25 +4831,25 @@
         <v>120</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K97" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4889,16 +4876,16 @@
         <v>120</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -4934,16 +4921,16 @@
         <v>120</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -4979,16 +4966,16 @@
         <v>120</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -5027,13 +5014,13 @@
         <v>124</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -5069,16 +5056,16 @@
         <v>120</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -5114,16 +5101,16 @@
         <v>120</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
@@ -5159,16 +5146,16 @@
         <v>120</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -5204,16 +5191,16 @@
         <v>120</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -5252,13 +5239,13 @@
         <v>124</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -5294,16 +5281,16 @@
         <v>120</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -5339,16 +5326,16 @@
         <v>120</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -5384,25 +5371,25 @@
         <v>120</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K109" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5416,16 @@
         <v>120</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -5477,13 +5464,13 @@
         <v>124</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -5519,16 +5506,16 @@
         <v>120</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -5564,16 +5551,16 @@
         <v>120</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -5609,16 +5596,16 @@
         <v>120</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -5654,16 +5641,16 @@
         <v>120</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -5702,13 +5689,13 @@
         <v>124</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -5744,16 +5731,16 @@
         <v>120</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
@@ -5789,16 +5776,16 @@
         <v>120</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
@@ -5834,16 +5821,16 @@
         <v>120</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -5879,16 +5866,16 @@
         <v>120</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
@@ -5924,25 +5911,25 @@
         <v>120</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K121" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -5969,16 +5956,16 @@
         <v>120</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -6014,16 +6001,16 @@
         <v>120</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -6059,16 +6046,16 @@
         <v>120</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -6104,16 +6091,16 @@
         <v>120</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -6152,13 +6139,13 @@
         <v>124</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -6194,16 +6181,16 @@
         <v>120</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -6239,16 +6226,16 @@
         <v>120</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -6284,16 +6271,16 @@
         <v>120</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6316,16 @@
         <v>120</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -6377,13 +6364,13 @@
         <v>124</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -6419,16 +6406,16 @@
         <v>120</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -6464,25 +6451,25 @@
         <v>120</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -6509,16 +6496,16 @@
         <v>120</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -6554,16 +6541,16 @@
         <v>120</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -6602,13 +6589,13 @@
         <v>124</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -6644,16 +6631,16 @@
         <v>120</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -6689,16 +6676,16 @@
         <v>120</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -6734,16 +6721,16 @@
         <v>120</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -6779,16 +6766,16 @@
         <v>120</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -6827,13 +6814,13 @@
         <v>124</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -6869,16 +6856,16 @@
         <v>120</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -6914,16 +6901,16 @@
         <v>120</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -6959,16 +6946,16 @@
         <v>120</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -7004,25 +6991,25 @@
         <v>120</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K145" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -7052,13 +7039,13 @@
         <v>124</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -7094,16 +7081,16 @@
         <v>120</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -7139,16 +7126,16 @@
         <v>120</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -7184,16 +7171,16 @@
         <v>120</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -7229,16 +7216,16 @@
         <v>120</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -7277,13 +7264,13 @@
         <v>124</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -7319,16 +7306,16 @@
         <v>120</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -7364,16 +7351,16 @@
         <v>120</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -7409,16 +7396,16 @@
         <v>120</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -7454,16 +7441,16 @@
         <v>120</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -7502,13 +7489,13 @@
         <v>124</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -7544,25 +7531,25 @@
         <v>120</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K157" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -7589,16 +7576,16 @@
         <v>120</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -7634,16 +7621,16 @@
         <v>120</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -7679,16 +7666,16 @@
         <v>120</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -7724,16 +7711,16 @@
         <v>120</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G161" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -7769,16 +7756,16 @@
         <v>120</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G162" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
@@ -7814,16 +7801,16 @@
         <v>120</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G163" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -7859,16 +7846,16 @@
         <v>120</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -7904,16 +7891,16 @@
         <v>120</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
@@ -7952,13 +7939,13 @@
         <v>124</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
@@ -7994,16 +7981,16 @@
         <v>120</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -8039,16 +8026,16 @@
         <v>120</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
@@ -8084,25 +8071,25 @@
         <v>120</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K169" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8116,16 @@
         <v>120</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
@@ -8177,13 +8164,13 @@
         <v>124</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -8219,16 +8206,16 @@
         <v>120</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
@@ -8264,16 +8251,16 @@
         <v>120</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -8309,16 +8296,16 @@
         <v>120</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
@@ -8354,16 +8341,16 @@
         <v>120</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
@@ -8402,13 +8389,13 @@
         <v>124</v>
       </c>
       <c r="G176" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
@@ -8444,16 +8431,16 @@
         <v>120</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
@@ -8489,16 +8476,16 @@
         <v>120</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
@@ -8534,16 +8521,16 @@
         <v>120</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
@@ -8579,16 +8566,16 @@
         <v>120</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
@@ -8627,22 +8614,22 @@
         <v>124</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K181" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -8669,16 +8656,16 @@
         <v>120</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
@@ -8714,16 +8701,16 @@
         <v>120</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G183" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
@@ -8759,16 +8746,16 @@
         <v>120</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
@@ -8804,16 +8791,16 @@
         <v>120</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
@@ -8852,13 +8839,13 @@
         <v>124</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
@@ -8894,16 +8881,16 @@
         <v>120</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G187" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
@@ -8939,16 +8926,16 @@
         <v>120</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
@@ -8984,16 +8971,16 @@
         <v>120</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
@@ -9029,16 +9016,16 @@
         <v>120</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
@@ -9077,13 +9064,13 @@
         <v>124</v>
       </c>
       <c r="G191" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
@@ -9119,16 +9106,16 @@
         <v>120</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G192" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
@@ -9164,25 +9151,25 @@
         <v>120</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K193" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -9209,16 +9196,16 @@
         <v>120</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G194" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
@@ -9254,16 +9241,16 @@
         <v>120</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
@@ -9302,13 +9289,13 @@
         <v>124</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
@@ -9344,16 +9331,16 @@
         <v>120</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
@@ -9389,16 +9376,16 @@
         <v>120</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G198" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
@@ -9434,16 +9421,16 @@
         <v>120</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G199" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
@@ -9479,16 +9466,16 @@
         <v>120</v>
       </c>
       <c r="F200" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G200" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
@@ -9524,16 +9511,16 @@
         <v>120</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
@@ -9569,16 +9556,16 @@
         <v>120</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
@@ -9614,16 +9601,16 @@
         <v>120</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G203" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
@@ -9659,16 +9646,16 @@
         <v>120</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
@@ -9704,25 +9691,25 @@
         <v>120</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K205" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -9752,13 +9739,13 @@
         <v>124</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
@@ -9794,16 +9781,16 @@
         <v>120</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G207" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
@@ -9839,16 +9826,16 @@
         <v>120</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G208" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
@@ -9884,16 +9871,16 @@
         <v>120</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G209" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
@@ -9929,16 +9916,16 @@
         <v>120</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
@@ -9977,13 +9964,13 @@
         <v>124</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
@@ -10019,16 +10006,16 @@
         <v>120</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G212" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
@@ -10064,16 +10051,16 @@
         <v>120</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G213" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
@@ -10109,16 +10096,16 @@
         <v>120</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G214" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
@@ -10154,16 +10141,16 @@
         <v>120</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
@@ -10202,13 +10189,13 @@
         <v>124</v>
       </c>
       <c r="G216" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
@@ -10244,25 +10231,25 @@
         <v>120</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K217" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -10289,16 +10276,16 @@
         <v>120</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G218" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
@@ -10334,16 +10321,16 @@
         <v>120</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G219" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
@@ -10379,16 +10366,16 @@
         <v>120</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G220" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
@@ -10427,13 +10414,13 @@
         <v>124</v>
       </c>
       <c r="G221" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
@@ -10469,16 +10456,16 @@
         <v>120</v>
       </c>
       <c r="F222" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G222" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
@@ -10514,16 +10501,16 @@
         <v>120</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G223" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
@@ -10559,16 +10546,16 @@
         <v>120</v>
       </c>
       <c r="F224" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G224" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
@@ -10604,16 +10591,16 @@
         <v>120</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G225" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
@@ -10652,13 +10639,13 @@
         <v>124</v>
       </c>
       <c r="G226" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
@@ -10694,16 +10681,16 @@
         <v>120</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G227" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
@@ -10739,16 +10726,16 @@
         <v>120</v>
       </c>
       <c r="F228" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G228" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
@@ -10784,25 +10771,25 @@
         <v>120</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G229" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K229" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -10829,16 +10816,16 @@
         <v>120</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G230" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
@@ -10877,13 +10864,13 @@
         <v>124</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
@@ -10919,16 +10906,16 @@
         <v>120</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G232" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
@@ -10964,16 +10951,16 @@
         <v>120</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
@@ -11009,16 +10996,16 @@
         <v>120</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G234" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
@@ -11054,16 +11041,16 @@
         <v>120</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G235" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
@@ -11102,13 +11089,13 @@
         <v>124</v>
       </c>
       <c r="G236" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
@@ -11144,16 +11131,16 @@
         <v>120</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
@@ -11189,16 +11176,16 @@
         <v>120</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G238" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
@@ -11234,16 +11221,16 @@
         <v>120</v>
       </c>
       <c r="F239" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G239" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
@@ -11279,16 +11266,16 @@
         <v>120</v>
       </c>
       <c r="F240" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G240" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
@@ -11324,25 +11311,25 @@
         <v>120</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G241" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K241" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K241" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -11369,16 +11356,16 @@
         <v>120</v>
       </c>
       <c r="F242" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G242" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H242" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
@@ -11414,16 +11401,16 @@
         <v>120</v>
       </c>
       <c r="F243" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G243" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
@@ -11459,16 +11446,16 @@
         <v>120</v>
       </c>
       <c r="F244" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G244" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H244" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
@@ -11504,16 +11491,16 @@
         <v>120</v>
       </c>
       <c r="F245" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G245" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
@@ -11552,13 +11539,13 @@
         <v>124</v>
       </c>
       <c r="G246" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
@@ -11594,16 +11581,16 @@
         <v>120</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
@@ -11639,16 +11626,16 @@
         <v>120</v>
       </c>
       <c r="F248" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G248" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H248" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
@@ -11684,16 +11671,16 @@
         <v>120</v>
       </c>
       <c r="F249" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G249" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
@@ -11729,16 +11716,16 @@
         <v>120</v>
       </c>
       <c r="F250" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G250" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
@@ -11777,13 +11764,13 @@
         <v>124</v>
       </c>
       <c r="G251" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H251" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
@@ -11819,16 +11806,16 @@
         <v>120</v>
       </c>
       <c r="F252" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G252" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
@@ -11864,25 +11851,25 @@
         <v>120</v>
       </c>
       <c r="F253" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G253" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H253" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K253" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K253" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -11909,16 +11896,16 @@
         <v>120</v>
       </c>
       <c r="F254" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G254" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H254" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
@@ -11954,16 +11941,16 @@
         <v>120</v>
       </c>
       <c r="F255" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G255" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H255" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
@@ -12002,13 +11989,13 @@
         <v>124</v>
       </c>
       <c r="G256" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H256" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I256" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
@@ -12044,16 +12031,16 @@
         <v>120</v>
       </c>
       <c r="F257" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G257" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H257" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
@@ -12089,16 +12076,16 @@
         <v>120</v>
       </c>
       <c r="F258" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G258" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
@@ -12134,16 +12121,16 @@
         <v>120</v>
       </c>
       <c r="F259" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G259" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H259" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
@@ -12179,16 +12166,16 @@
         <v>120</v>
       </c>
       <c r="F260" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G260" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H260" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
@@ -12227,13 +12214,13 @@
         <v>124</v>
       </c>
       <c r="G261" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H261" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
@@ -12269,16 +12256,16 @@
         <v>120</v>
       </c>
       <c r="F262" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G262" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
@@ -12314,16 +12301,16 @@
         <v>120</v>
       </c>
       <c r="F263" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G263" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H263" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
@@ -12359,16 +12346,16 @@
         <v>120</v>
       </c>
       <c r="F264" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G264" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H264" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
@@ -12404,25 +12391,25 @@
         <v>120</v>
       </c>
       <c r="F265" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G265" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K265" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K265" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -12452,13 +12439,13 @@
         <v>124</v>
       </c>
       <c r="G266" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H266" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
@@ -12494,16 +12481,16 @@
         <v>120</v>
       </c>
       <c r="F267" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G267" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H267" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I267" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
@@ -12539,16 +12526,16 @@
         <v>120</v>
       </c>
       <c r="F268" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G268" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H268" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
@@ -12584,16 +12571,16 @@
         <v>120</v>
       </c>
       <c r="F269" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G269" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H269" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I269" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
@@ -12629,16 +12616,16 @@
         <v>120</v>
       </c>
       <c r="F270" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G270" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H270" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
@@ -12677,13 +12664,13 @@
         <v>124</v>
       </c>
       <c r="G271" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H271" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
@@ -12719,16 +12706,16 @@
         <v>120</v>
       </c>
       <c r="F272" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G272" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H272" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
@@ -12764,16 +12751,16 @@
         <v>120</v>
       </c>
       <c r="F273" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G273" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H273" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
@@ -12809,16 +12796,16 @@
         <v>120</v>
       </c>
       <c r="F274" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G274" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H274" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
@@ -12854,16 +12841,16 @@
         <v>120</v>
       </c>
       <c r="F275" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G275" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H275" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
@@ -12902,13 +12889,13 @@
         <v>124</v>
       </c>
       <c r="G276" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H276" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I276" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
@@ -12944,25 +12931,25 @@
         <v>120</v>
       </c>
       <c r="F277" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G277" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H277" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K277" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K277" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -12989,16 +12976,16 @@
         <v>120</v>
       </c>
       <c r="F278" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G278" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H278" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
@@ -13034,16 +13021,16 @@
         <v>120</v>
       </c>
       <c r="F279" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G279" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H279" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
@@ -13079,16 +13066,16 @@
         <v>120</v>
       </c>
       <c r="F280" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G280" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H280" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
@@ -13124,16 +13111,16 @@
         <v>120</v>
       </c>
       <c r="F281" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G281" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H281" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
@@ -13169,16 +13156,16 @@
         <v>120</v>
       </c>
       <c r="F282" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G282" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H282" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
@@ -13214,16 +13201,16 @@
         <v>120</v>
       </c>
       <c r="F283" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G283" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H283" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
@@ -13259,16 +13246,16 @@
         <v>120</v>
       </c>
       <c r="F284" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G284" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H284" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
@@ -13304,16 +13291,16 @@
         <v>120</v>
       </c>
       <c r="F285" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G285" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H285" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
@@ -13352,13 +13339,13 @@
         <v>124</v>
       </c>
       <c r="G286" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H286" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
@@ -13394,16 +13381,16 @@
         <v>120</v>
       </c>
       <c r="F287" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G287" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H287" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
@@ -13439,16 +13426,16 @@
         <v>120</v>
       </c>
       <c r="F288" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G288" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H288" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
@@ -13484,25 +13471,25 @@
         <v>120</v>
       </c>
       <c r="F289" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G289" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H289" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K289" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K289" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -13529,16 +13516,16 @@
         <v>120</v>
       </c>
       <c r="F290" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G290" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H290" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
@@ -13577,13 +13564,13 @@
         <v>124</v>
       </c>
       <c r="G291" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H291" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
@@ -13619,16 +13606,16 @@
         <v>120</v>
       </c>
       <c r="F292" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G292" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H292" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
@@ -13664,16 +13651,16 @@
         <v>120</v>
       </c>
       <c r="F293" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G293" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H293" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
@@ -13709,16 +13696,16 @@
         <v>120</v>
       </c>
       <c r="F294" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G294" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H294" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
@@ -13754,16 +13741,16 @@
         <v>120</v>
       </c>
       <c r="F295" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G295" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H295" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
@@ -13802,13 +13789,13 @@
         <v>124</v>
       </c>
       <c r="G296" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H296" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
@@ -13844,16 +13831,16 @@
         <v>120</v>
       </c>
       <c r="F297" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G297" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H297" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
@@ -13889,16 +13876,16 @@
         <v>120</v>
       </c>
       <c r="F298" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G298" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H298" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
@@ -13934,16 +13921,16 @@
         <v>120</v>
       </c>
       <c r="F299" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G299" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H299" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
@@ -13979,16 +13966,16 @@
         <v>120</v>
       </c>
       <c r="F300" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G300" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H300" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
@@ -14027,22 +14014,22 @@
         <v>124</v>
       </c>
       <c r="G301" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H301" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K301" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K301" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -14069,16 +14056,16 @@
         <v>120</v>
       </c>
       <c r="F302" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G302" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H302" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
@@ -14114,16 +14101,16 @@
         <v>120</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G303" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H303" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
@@ -14159,16 +14146,16 @@
         <v>120</v>
       </c>
       <c r="F304" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G304" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H304" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
@@ -14204,16 +14191,16 @@
         <v>120</v>
       </c>
       <c r="F305" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G305" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H305" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
@@ -14252,13 +14239,13 @@
         <v>124</v>
       </c>
       <c r="G306" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H306" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
@@ -14294,16 +14281,16 @@
         <v>120</v>
       </c>
       <c r="F307" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G307" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H307" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
@@ -14339,16 +14326,16 @@
         <v>120</v>
       </c>
       <c r="F308" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G308" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H308" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
@@ -14384,16 +14371,16 @@
         <v>120</v>
       </c>
       <c r="F309" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G309" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H309" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J309" s="2" t="inlineStr">
         <is>
@@ -14429,16 +14416,16 @@
         <v>120</v>
       </c>
       <c r="F310" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G310" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H310" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
@@ -14477,13 +14464,13 @@
         <v>124</v>
       </c>
       <c r="G311" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H311" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
@@ -14519,16 +14506,16 @@
         <v>120</v>
       </c>
       <c r="F312" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G312" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H312" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
@@ -14564,25 +14551,25 @@
         <v>120</v>
       </c>
       <c r="F313" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G313" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H313" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K313" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K313" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -14609,16 +14596,16 @@
         <v>120</v>
       </c>
       <c r="F314" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G314" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H314" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
@@ -14654,16 +14641,16 @@
         <v>120</v>
       </c>
       <c r="F315" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G315" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H315" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J315" s="2" t="inlineStr">
         <is>
@@ -14702,13 +14689,13 @@
         <v>124</v>
       </c>
       <c r="G316" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H316" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
@@ -14744,16 +14731,16 @@
         <v>120</v>
       </c>
       <c r="F317" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G317" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H317" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
@@ -14789,16 +14776,16 @@
         <v>120</v>
       </c>
       <c r="F318" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G318" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H318" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
@@ -14834,16 +14821,16 @@
         <v>120</v>
       </c>
       <c r="F319" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G319" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H319" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J319" s="2" t="inlineStr">
         <is>
@@ -14879,16 +14866,16 @@
         <v>120</v>
       </c>
       <c r="F320" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G320" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H320" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J320" s="2" t="inlineStr">
         <is>
@@ -14924,16 +14911,16 @@
         <v>120</v>
       </c>
       <c r="F321" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G321" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H321" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J321" s="2" t="inlineStr">
         <is>
@@ -14969,16 +14956,16 @@
         <v>120</v>
       </c>
       <c r="F322" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G322" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H322" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
@@ -15014,16 +15001,16 @@
         <v>120</v>
       </c>
       <c r="F323" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G323" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H323" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J323" s="2" t="inlineStr">
         <is>
@@ -15059,16 +15046,16 @@
         <v>120</v>
       </c>
       <c r="F324" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G324" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H324" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
@@ -15104,25 +15091,25 @@
         <v>120</v>
       </c>
       <c r="F325" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G325" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H325" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J325" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K325" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K325" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -15152,13 +15139,13 @@
         <v>124</v>
       </c>
       <c r="G326" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H326" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I326" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
@@ -15194,16 +15181,16 @@
         <v>120</v>
       </c>
       <c r="F327" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G327" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H327" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I327" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J327" s="2" t="inlineStr">
         <is>
@@ -15239,16 +15226,16 @@
         <v>120</v>
       </c>
       <c r="F328" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G328" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H328" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I328" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J328" s="2" t="inlineStr">
         <is>
@@ -15284,16 +15271,16 @@
         <v>120</v>
       </c>
       <c r="F329" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G329" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H329" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I329" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J329" s="2" t="inlineStr">
         <is>
@@ -15329,16 +15316,16 @@
         <v>120</v>
       </c>
       <c r="F330" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G330" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H330" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I330" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J330" s="2" t="inlineStr">
         <is>
@@ -15377,13 +15364,13 @@
         <v>124</v>
       </c>
       <c r="G331" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H331" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I331" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
@@ -15419,16 +15406,16 @@
         <v>120</v>
       </c>
       <c r="F332" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G332" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H332" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I332" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
@@ -15464,16 +15451,16 @@
         <v>120</v>
       </c>
       <c r="F333" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G333" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H333" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I333" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
@@ -15509,16 +15496,16 @@
         <v>120</v>
       </c>
       <c r="F334" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G334" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H334" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I334" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
@@ -15554,16 +15541,16 @@
         <v>120</v>
       </c>
       <c r="F335" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G335" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H335" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I335" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J335" s="2" t="inlineStr">
         <is>
@@ -15602,13 +15589,13 @@
         <v>124</v>
       </c>
       <c r="G336" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H336" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I336" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J336" s="2" t="inlineStr">
         <is>
@@ -15644,25 +15631,25 @@
         <v>120</v>
       </c>
       <c r="F337" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G337" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H337" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I337" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K337" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K337" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -15689,16 +15676,16 @@
         <v>120</v>
       </c>
       <c r="F338" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G338" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H338" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I338" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
@@ -15734,16 +15721,16 @@
         <v>120</v>
       </c>
       <c r="F339" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G339" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H339" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I339" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J339" s="2" t="inlineStr">
         <is>
@@ -15779,16 +15766,16 @@
         <v>120</v>
       </c>
       <c r="F340" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G340" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H340" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I340" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
@@ -15827,13 +15814,13 @@
         <v>124</v>
       </c>
       <c r="G341" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H341" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I341" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
@@ -15869,16 +15856,16 @@
         <v>120</v>
       </c>
       <c r="F342" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G342" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H342" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I342" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
@@ -15914,16 +15901,16 @@
         <v>120</v>
       </c>
       <c r="F343" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G343" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H343" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I343" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J343" s="2" t="inlineStr">
         <is>
@@ -15959,16 +15946,16 @@
         <v>120</v>
       </c>
       <c r="F344" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G344" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H344" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I344" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J344" s="2" t="inlineStr">
         <is>
@@ -16004,16 +15991,16 @@
         <v>120</v>
       </c>
       <c r="F345" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G345" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H345" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I345" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J345" s="2" t="inlineStr">
         <is>
@@ -16052,13 +16039,13 @@
         <v>124</v>
       </c>
       <c r="G346" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H346" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I346" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
@@ -16094,16 +16081,16 @@
         <v>120</v>
       </c>
       <c r="F347" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G347" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H347" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I347" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J347" s="2" t="inlineStr">
         <is>
@@ -16139,16 +16126,16 @@
         <v>120</v>
       </c>
       <c r="F348" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G348" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H348" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I348" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J348" s="2" t="inlineStr">
         <is>
@@ -16184,25 +16171,25 @@
         <v>120</v>
       </c>
       <c r="F349" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G349" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H349" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I349" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J349" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K349" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K349" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -16229,16 +16216,16 @@
         <v>120</v>
       </c>
       <c r="F350" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G350" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H350" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I350" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J350" s="2" t="inlineStr">
         <is>
@@ -16277,13 +16264,13 @@
         <v>124</v>
       </c>
       <c r="G351" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H351" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I351" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J351" s="2" t="inlineStr">
         <is>
@@ -16319,16 +16306,16 @@
         <v>120</v>
       </c>
       <c r="F352" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G352" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H352" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I352" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J352" s="2" t="inlineStr">
         <is>
@@ -16364,16 +16351,16 @@
         <v>120</v>
       </c>
       <c r="F353" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G353" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H353" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I353" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J353" s="2" t="inlineStr">
         <is>
@@ -16409,16 +16396,16 @@
         <v>120</v>
       </c>
       <c r="F354" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G354" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H354" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I354" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
@@ -16454,16 +16441,16 @@
         <v>120</v>
       </c>
       <c r="F355" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G355" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H355" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I355" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J355" s="2" t="inlineStr">
         <is>
@@ -16502,13 +16489,13 @@
         <v>124</v>
       </c>
       <c r="G356" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H356" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I356" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J356" s="2" t="inlineStr">
         <is>
@@ -16544,16 +16531,16 @@
         <v>120</v>
       </c>
       <c r="F357" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G357" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H357" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I357" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J357" s="2" t="inlineStr">
         <is>
@@ -16589,16 +16576,16 @@
         <v>120</v>
       </c>
       <c r="F358" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G358" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H358" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I358" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
@@ -16634,16 +16621,16 @@
         <v>120</v>
       </c>
       <c r="F359" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G359" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H359" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I359" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
@@ -16679,16 +16666,16 @@
         <v>120</v>
       </c>
       <c r="F360" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G360" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H360" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I360" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J360" s="2" t="inlineStr">
         <is>
@@ -16724,25 +16711,25 @@
         <v>120</v>
       </c>
       <c r="F361" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G361" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H361" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I361" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J361" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K361" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K361" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -16769,16 +16756,16 @@
         <v>120</v>
       </c>
       <c r="F362" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G362" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H362" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I362" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J362" s="2" t="inlineStr">
         <is>
@@ -16814,16 +16801,16 @@
         <v>120</v>
       </c>
       <c r="F363" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G363" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H363" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I363" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J363" s="2" t="inlineStr">
         <is>
@@ -16859,16 +16846,16 @@
         <v>120</v>
       </c>
       <c r="F364" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G364" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H364" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I364" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J364" s="2" t="inlineStr">
         <is>
@@ -16904,16 +16891,16 @@
         <v>120</v>
       </c>
       <c r="F365" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G365" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H365" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I365" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J365" s="2" t="inlineStr">
         <is>
@@ -16952,13 +16939,13 @@
         <v>124</v>
       </c>
       <c r="G366" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H366" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I366" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J366" s="2" t="inlineStr">
         <is>
@@ -16994,16 +16981,16 @@
         <v>120</v>
       </c>
       <c r="F367" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G367" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H367" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I367" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J367" s="2" t="inlineStr">
         <is>
@@ -17039,16 +17026,16 @@
         <v>120</v>
       </c>
       <c r="F368" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G368" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H368" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I368" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
@@ -17084,16 +17071,16 @@
         <v>120</v>
       </c>
       <c r="F369" s="2" t="n">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="G369" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H369" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I369" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J369" s="2" t="inlineStr">
         <is>
@@ -17129,16 +17116,16 @@
         <v>120</v>
       </c>
       <c r="F370" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G370" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H370" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I370" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J370" s="2" t="inlineStr">
         <is>
@@ -17177,13 +17164,13 @@
         <v>124</v>
       </c>
       <c r="G371" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H371" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I371" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J371" s="2" t="inlineStr">
         <is>
@@ -17219,16 +17206,16 @@
         <v>120</v>
       </c>
       <c r="F372" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G372" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H372" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I372" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
@@ -17264,25 +17251,25 @@
         <v>120</v>
       </c>
       <c r="F373" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G373" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H373" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I373" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K373" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K373" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -17309,16 +17296,16 @@
         <v>120</v>
       </c>
       <c r="F374" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G374" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H374" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I374" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
@@ -17354,16 +17341,16 @@
         <v>120</v>
       </c>
       <c r="F375" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G375" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H375" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I375" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J375" s="2" t="inlineStr">
         <is>
@@ -17402,13 +17389,13 @@
         <v>124</v>
       </c>
       <c r="G376" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H376" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I376" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J376" s="2" t="inlineStr">
         <is>
@@ -17444,16 +17431,16 @@
         <v>120</v>
       </c>
       <c r="F377" s="2" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="G377" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H377" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I377" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
@@ -17489,16 +17476,16 @@
         <v>120</v>
       </c>
       <c r="F378" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G378" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H378" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I378" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J378" s="2" t="inlineStr">
         <is>
@@ -17534,16 +17521,16 @@
         <v>120</v>
       </c>
       <c r="F379" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G379" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H379" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I379" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J379" s="2" t="inlineStr">
         <is>
@@ -17579,16 +17566,16 @@
         <v>120</v>
       </c>
       <c r="F380" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G380" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H380" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I380" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J380" s="2" t="inlineStr">
         <is>
@@ -17627,13 +17614,13 @@
         <v>124</v>
       </c>
       <c r="G381" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H381" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I381" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J381" s="2" t="inlineStr">
         <is>
@@ -17669,16 +17656,16 @@
         <v>120</v>
       </c>
       <c r="F382" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G382" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H382" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I382" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
@@ -17714,16 +17701,16 @@
         <v>120</v>
       </c>
       <c r="F383" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G383" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H383" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I383" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
@@ -17759,16 +17746,16 @@
         <v>120</v>
       </c>
       <c r="F384" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G384" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H384" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I384" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
@@ -17804,25 +17791,25 @@
         <v>120</v>
       </c>
       <c r="F385" s="2" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G385" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H385" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I385" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K385" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K385" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -17852,13 +17839,13 @@
         <v>124</v>
       </c>
       <c r="G386" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H386" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I386" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J386" s="2" t="inlineStr">
         <is>
@@ -17894,16 +17881,16 @@
         <v>120</v>
       </c>
       <c r="F387" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G387" s="2" t="n">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="H387" s="2" t="n">
-        <v>410</v>
+        <v>284</v>
       </c>
       <c r="I387" s="2" t="n">
-        <v>530</v>
+        <v>334</v>
       </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
@@ -17939,16 +17926,16 @@
         <v>120</v>
       </c>
       <c r="F388" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G388" s="2" t="n">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="H388" s="2" t="n">
-        <v>415</v>
+        <v>288</v>
       </c>
       <c r="I388" s="2" t="n">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
@@ -17984,16 +17971,16 @@
         <v>120</v>
       </c>
       <c r="F389" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G389" s="2" t="n">
-        <v>310</v>
+        <v>232</v>
       </c>
       <c r="H389" s="2" t="n">
-        <v>420</v>
+        <v>292</v>
       </c>
       <c r="I389" s="2" t="n">
-        <v>540</v>
+        <v>342</v>
       </c>
       <c r="J389" s="2" t="inlineStr">
         <is>
@@ -18029,16 +18016,16 @@
         <v>120</v>
       </c>
       <c r="F390" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G390" s="2" t="n">
-        <v>315</v>
+        <v>236</v>
       </c>
       <c r="H390" s="2" t="n">
-        <v>425</v>
+        <v>296</v>
       </c>
       <c r="I390" s="2" t="n">
-        <v>545</v>
+        <v>346</v>
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
@@ -18077,13 +18064,13 @@
         <v>124</v>
       </c>
       <c r="G391" s="2" t="n">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="H391" s="2" t="n">
-        <v>355</v>
+        <v>240</v>
       </c>
       <c r="I391" s="2" t="n">
-        <v>475</v>
+        <v>290</v>
       </c>
       <c r="J391" s="2" t="inlineStr">
         <is>
@@ -18119,16 +18106,16 @@
         <v>120</v>
       </c>
       <c r="F392" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G392" s="2" t="n">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="H392" s="2" t="n">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="I392" s="2" t="n">
-        <v>480</v>
+        <v>294</v>
       </c>
       <c r="J392" s="2" t="inlineStr">
         <is>
@@ -18164,16 +18151,16 @@
         <v>120</v>
       </c>
       <c r="F393" s="2" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G393" s="2" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="H393" s="2" t="n">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="I393" s="2" t="n">
-        <v>485</v>
+        <v>298</v>
       </c>
       <c r="J393" s="2" t="inlineStr">
         <is>
@@ -18209,16 +18196,16 @@
         <v>120</v>
       </c>
       <c r="F394" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G394" s="2" t="n">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="H394" s="2" t="n">
-        <v>370</v>
+        <v>252</v>
       </c>
       <c r="I394" s="2" t="n">
-        <v>490</v>
+        <v>302</v>
       </c>
       <c r="J394" s="2" t="inlineStr">
         <is>
@@ -18254,16 +18241,16 @@
         <v>120</v>
       </c>
       <c r="F395" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G395" s="2" t="n">
-        <v>265</v>
+        <v>196</v>
       </c>
       <c r="H395" s="2" t="n">
-        <v>375</v>
+        <v>256</v>
       </c>
       <c r="I395" s="2" t="n">
-        <v>495</v>
+        <v>306</v>
       </c>
       <c r="J395" s="2" t="inlineStr">
         <is>
@@ -18302,13 +18289,13 @@
         <v>124</v>
       </c>
       <c r="G396" s="2" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H396" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="I396" s="2" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
@@ -18344,25 +18331,25 @@
         <v>120</v>
       </c>
       <c r="F397" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G397" s="2" t="n">
-        <v>275</v>
+        <v>204</v>
       </c>
       <c r="H397" s="2" t="n">
-        <v>385</v>
+        <v>264</v>
       </c>
       <c r="I397" s="2" t="n">
-        <v>505</v>
+        <v>314</v>
       </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="K397" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K397" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -18389,16 +18376,16 @@
         <v>120</v>
       </c>
       <c r="F398" s="2" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G398" s="2" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
       <c r="H398" s="2" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="I398" s="2" t="n">
-        <v>510</v>
+        <v>318</v>
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
@@ -18434,16 +18421,16 @@
         <v>120</v>
       </c>
       <c r="F399" s="2" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G399" s="2" t="n">
-        <v>285</v>
+        <v>212</v>
       </c>
       <c r="H399" s="2" t="n">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="I399" s="2" t="n">
-        <v>515</v>
+        <v>322</v>
       </c>
       <c r="J399" s="2" t="inlineStr">
         <is>
@@ -18479,16 +18466,16 @@
         <v>120</v>
       </c>
       <c r="F400" s="2" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G400" s="2" t="n">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="H400" s="2" t="n">
-        <v>400</v>
+        <v>276</v>
       </c>
       <c r="I400" s="2" t="n">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="J400" s="2" t="inlineStr">
         <is>
@@ -18524,16 +18511,16 @@
         <v>120</v>
       </c>
       <c r="F401" s="2" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="G401" s="2" t="n">
-        <v>295</v>
+        <v>220</v>
       </c>
       <c r="H401" s="2" t="n">
-        <v>405</v>
+        <v>280</v>
       </c>
       <c r="I401" s="2" t="n">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="J401" s="2" t="inlineStr">
         <is>
